--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/RogueGlobalConfig.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/RogueGlobalConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -62,6 +62,9 @@
     <t>CorpseButtonTextId</t>
   </si>
   <si>
+    <t>DefaultMonsterCorpseLootBoxUnitConfigId</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -74,6 +77,9 @@
     <t>##group</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -105,6 +111,9 @@
   </si>
   <si>
     <t>尸体盒交互按钮文案ID</t>
+  </si>
+  <si>
+    <t>默认怪物尸体盒UnitConfigId</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1072,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="12.875" customWidth="1"/>
@@ -1106,80 +1115,92 @@
       <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="0" t="s">
-        <v>12</v>
+      <c r="L2" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -1212,6 +1233,9 @@
       </c>
       <c r="K5" s="0">
         <v>0</v>
+      </c>
+      <c r="L5" s="0">
+        <v>1002</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/RogueGlobalConfig.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/RogueGlobalConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -65,6 +65,9 @@
     <t>DefaultMonsterCorpseLootBoxUnitConfigId</t>
   </si>
   <si>
+    <t>AutoSecureMinValuePerGrid</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -114,6 +117,9 @@
   </si>
   <si>
     <t>默认怪物尸体盒UnitConfigId</t>
+  </si>
+  <si>
+    <t>自动拾取进安全格的单格最小价值</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="12.875" customWidth="1"/>
@@ -1118,89 +1124,101 @@
       <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="0" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="0" t="s">
-        <v>13</v>
-      </c>
       <c r="L2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M2" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="M4" s="0" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -1236,6 +1254,9 @@
       </c>
       <c r="L5" s="0">
         <v>1002</v>
+      </c>
+      <c r="M5" s="0">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
